--- a/artfynd/A 49276-2021 artfynd.xlsx
+++ b/artfynd/A 49276-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49276-2021 artfynd.xlsx
+++ b/artfynd/A 49276-2021 artfynd.xlsx
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96632291</v>
+        <v>96632494</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555403.8492052711</v>
+        <v>555327</v>
       </c>
       <c r="R2" t="n">
-        <v>6267704.390193205</v>
+        <v>6267637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,24 +746,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021 på två olika lågor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -804,51 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96632534</v>
+        <v>96632933</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555369.0043482085</v>
+        <v>555335</v>
       </c>
       <c r="R3" t="n">
-        <v>6267665.899290775</v>
+        <v>6267651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,19 +852,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -934,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96631894</v>
+        <v>96897104</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555428.7246033207</v>
+        <v>555347</v>
       </c>
       <c r="R4" t="n">
-        <v>6267618.726984423</v>
+        <v>6267727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1055,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96632933</v>
+        <v>96897114</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555335.5049691289</v>
+        <v>555318</v>
       </c>
       <c r="R5" t="n">
-        <v>6267651.128400446</v>
+        <v>6267711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,22 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1176,51 +1099,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96632352</v>
+        <v>97104018</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555341.4776157949</v>
+        <v>555324</v>
       </c>
       <c r="R6" t="n">
-        <v>6267743.25901562</v>
+        <v>6267628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,27 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,8 +1181,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>barklös granlåga</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # barklös granlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1305,15 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96632226</v>
+        <v>96632265</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,26 +1231,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1348,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555423.7082941632</v>
+        <v>555412</v>
       </c>
       <c r="R7" t="n">
-        <v>6267706.304520692</v>
+        <v>6267696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,19 +1300,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1425,15 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96632265</v>
+        <v>96632361</v>
       </c>
       <c r="B8" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555411.6891415737</v>
+        <v>555347</v>
       </c>
       <c r="R8" t="n">
-        <v>6267696.224928204</v>
+        <v>6267713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1510,19 +1414,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1554,51 +1448,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96642266</v>
+        <v>96632389</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1606,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555335.5049691289</v>
+        <v>555302</v>
       </c>
       <c r="R9" t="n">
-        <v>6267651.128400446</v>
+        <v>6267697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,19 +1528,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,42 +1562,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96632494</v>
+        <v>96632534</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1721,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555326.2972762173</v>
+        <v>555369</v>
       </c>
       <c r="R10" t="n">
-        <v>6267637.227253479</v>
+        <v>6267666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,24 +1642,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 49276-2021 på två olika lågor</t>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,51 +1677,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96632354</v>
+        <v>96632226</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1851,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555332.0100848441</v>
+        <v>555423</v>
       </c>
       <c r="R11" t="n">
-        <v>6267749.1981601</v>
+        <v>6267707</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,19 +1748,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1928,51 +1782,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96632323</v>
+        <v>96631894</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1980,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555378.0310887995</v>
+        <v>555428</v>
       </c>
       <c r="R12" t="n">
-        <v>6267693.578394791</v>
+        <v>6267618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2013,24 +1853,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,6 +1869,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2057,51 +1888,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96632532</v>
+        <v>96642266</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2109,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555369.0043482085</v>
+        <v>555335</v>
       </c>
       <c r="R13" t="n">
-        <v>6267665.899290775</v>
+        <v>6267651</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2144,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2154,12 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2189,12 +2010,7 @@
         <v>96642276</v>
       </c>
       <c r="B14" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555335.5049691289</v>
+        <v>555335</v>
       </c>
       <c r="R14" t="n">
-        <v>6267651.128400446</v>
+        <v>6267651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2310,51 +2126,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96632361</v>
+        <v>96897129</v>
       </c>
       <c r="B15" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2362,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555346.8379668052</v>
+        <v>555318</v>
       </c>
       <c r="R15" t="n">
-        <v>6267713.564092278</v>
+        <v>6267711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2392,27 +2203,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2439,15 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96632319</v>
+        <v>96624335</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,14 +2265,10 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2491,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555384.5351138981</v>
+        <v>555390</v>
       </c>
       <c r="R16" t="n">
-        <v>6267703.034320265</v>
+        <v>6267712</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2521,27 +2308,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>avverkningsanmälan  A 49276-2021</t>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,6 +2327,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2568,47 +2346,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96632389</v>
+        <v>96632291</v>
       </c>
       <c r="B17" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2620,10 +2393,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555301.7634091571</v>
+        <v>555404</v>
       </c>
       <c r="R17" t="n">
-        <v>6267696.988241781</v>
+        <v>6267704</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2653,19 +2426,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2697,15 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96632439</v>
+        <v>96632319</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2732,7 +2490,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2749,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555308.545747662</v>
+        <v>555385</v>
       </c>
       <c r="R18" t="n">
-        <v>6267643.058041937</v>
+        <v>6267703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2782,24 +2540,14 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2808,7 +2556,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2827,15 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96624335</v>
+        <v>96632323</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2862,10 +2604,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2875,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555389.3896112281</v>
+        <v>555378</v>
       </c>
       <c r="R19" t="n">
-        <v>6267711.917381245</v>
+        <v>6267694</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2905,27 +2651,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2934,7 +2670,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2953,51 +2688,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96897129</v>
+        <v>96632439</v>
       </c>
       <c r="B20" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3005,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555318.7024559347</v>
+        <v>555308</v>
       </c>
       <c r="R20" t="n">
-        <v>6267710.990451365</v>
+        <v>6267643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3035,22 +2765,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan A 49276-2021</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3059,6 +2784,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3077,42 +2803,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96897114</v>
+        <v>96632532</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3120,10 +2850,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555318.7024559347</v>
+        <v>555369</v>
       </c>
       <c r="R21" t="n">
-        <v>6267710.990451365</v>
+        <v>6267666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,22 +2880,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3179,7 +2899,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3198,42 +2917,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96897104</v>
+        <v>97104024</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3241,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555347.2240126507</v>
+        <v>555317</v>
       </c>
       <c r="R22" t="n">
-        <v>6267726.246950923</v>
+        <v>6267633</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3271,27 +2994,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan A 49276-2021</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3319,15 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97104024</v>
+        <v>96632352</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3354,7 +3057,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3371,10 +3074,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555316.4072735655</v>
+        <v>555341</v>
       </c>
       <c r="R23" t="n">
-        <v>6267633.239108293</v>
+        <v>6267744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3401,22 +3104,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3425,7 +3123,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3444,42 +3141,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97104018</v>
+        <v>96632354</v>
       </c>
       <c r="B24" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3487,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555324.7560841559</v>
+        <v>555332</v>
       </c>
       <c r="R24" t="n">
-        <v>6267628.387537828</v>
+        <v>6267749</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3517,22 +3218,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan  A 49276-2021</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3541,29 +3237,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>barklös granlåga</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies # barklös granlåga</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">

--- a/artfynd/A 49276-2021 artfynd.xlsx
+++ b/artfynd/A 49276-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632933</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897114</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104018</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632265</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632361</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632389</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632534</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1779,6 +1829,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632226</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96631894</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96642266</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96642276</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2232,6 +2302,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897129</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2343,6 +2418,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96624335</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2457,6 +2537,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632291</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632319</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2685,6 +2775,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632323</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2799,6 +2894,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632352</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632354</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3028,6 +3133,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632439</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3142,6 +3252,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96632532</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3252,8 +3367,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97104024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>